--- a/光伏配储项目/电价数据/2026/绿洲站.xlsx
+++ b/光伏配储项目/电价数据/2026/绿洲站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51119</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.74603</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57484</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.58284</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51019</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5021100000000001</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45451</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42829</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42213</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41974</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40895</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39749</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39691</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38496</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41263</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41701</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39215</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41398</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42397</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27352</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11788</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09622</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.10529</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.09251000000000001</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.11538</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03831</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.08301</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.11275</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.10593</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.07529000000000001</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09013</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.06806999999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.02543</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14339</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21289</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22427</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.22869</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21441</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.08316</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.00046</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.24383</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.12253</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.25568</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.27044</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.25189</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.19266</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.27509</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5444500000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.42205</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.49147</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.69304</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39453</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.57961</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43121</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43675</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5676</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44984</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6037</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79577</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.62238</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.73677</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.9071699999999999</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41559</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58412</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.7020700000000001</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.47915</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.39898</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.62363</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6022999999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.48992</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48056</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.42959</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6905</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.05942</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.64946</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.61833</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.68183</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49703</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51751</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50464</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50473</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48689</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46893</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41811</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.48806</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.5584199999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.51393</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42841</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37145</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42261</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50843</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.22827</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.18277</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29818</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.47962</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.74714</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9630299999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.47823</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.54103</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.51683</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.45036</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.68629</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.50928</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.59399</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.41841</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28481</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.48031</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.41206</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.58512</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.44216</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.42056</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.48699</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.44787</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49336</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.5916399999999999</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.52438</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6701900000000001</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6416000000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.71727</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.44273</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.76191</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.46171</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.50287</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43211</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.45783</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43506</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42854</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37601</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50913</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.40888</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40562</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42866</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44426</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39652</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47382</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44448</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39486</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.23958</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.24645</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.2352</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20326</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.20973</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27029</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5092</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.44035</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.7469199999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.54173</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.49965</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.44327</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.43763</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.43674</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.46046</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.44495</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.51056</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.52162</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6051</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.56467</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.59929</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.45962</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.47806</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.44317</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43512</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45633</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.44224</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39306</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41739</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39714</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.39438</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34205</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.45394</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39286</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39207</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40131</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44911</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39706</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42078</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43123</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.25906</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.1336</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.24092</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.18825</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.27612</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.18877</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56313</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.39333</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.16462</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.17306</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.14239</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.18102</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47221</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16725</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37599</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.43171</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50648</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42117</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42118</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29345</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31032</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38212</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.15714</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.16825</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.15768</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.1533</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04477</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.16701</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.16226</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.14938</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02798</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04611999999999999</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.05378</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.10544</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.07156</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.06344</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.04499</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.12235</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04037</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04521</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.11478</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.03924</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03851</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04133</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04435</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.11422</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.10954</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21889</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.16232</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.18163</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05845</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04938</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00273</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.02592</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.24786</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03207</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09437000000000001</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29409</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38774</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46741</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41684</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35082</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.65347</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4453</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42256</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42249</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10252</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04342</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0449</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00641</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19934</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04584000000000001</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.10372</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.16531</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.02007</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04445</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05351</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04472</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04740999999999999</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04793</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19972</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.1427</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29489</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26872</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33532</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17234</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15859</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15942</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23609</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21398</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28089</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42818</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45647</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91406</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86245</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29597</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88707</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63152</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18666</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8684500000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5366000000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33042</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03261</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79062</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5298200000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7726000000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77725</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87673</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8736699999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49281</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39944</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44955</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20655</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87881</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62141</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5382100000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49756</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45576</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43706</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41458</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43355</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.3996499999999999</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58563</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4272</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59565</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60137</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.69089</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46843</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41766</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5803400000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45056</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87559</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.62749</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8574400000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.82723</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86146</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44051</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.53238</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.26631</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40963</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45185</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35333</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91816</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46467</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4079700000000001</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46405</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40949</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32282</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49934</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38732</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35779</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33811</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29053</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29746</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16598</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26219</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19891</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27723</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19297</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30216</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29899</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25561</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38535</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4434</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42317</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5955499999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8898200000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44442</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16134</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69996</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7908200000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66492</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57959</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45006</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50107</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42361</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50057</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43442</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41283</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42794</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43405</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42342</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025899999999999</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49472</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5490900000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24963</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14994</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27736</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02849</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26164</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25528</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28292</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.56992</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46224</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.8500599999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43642</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.45427</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32342</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42181</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39824</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28131</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27976</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27861</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22475</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.1409</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14466</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27984</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15236</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14159</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.13623</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14116</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13569</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24641</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13621</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25404</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.25475</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.13619</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.10289</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.1074</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10703</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.12471</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13511</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.1399</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27532</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34298</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39746</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38417</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44886</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39906</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45202</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43882</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43813</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44305</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44378</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39709</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34833</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53762</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46792</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42302</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41515</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39103</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27204</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26695</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19977</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24965</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24315</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27078</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29354</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28629</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24225</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28582</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32383</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40619</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.26008</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41508</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35999</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41755</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39508</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43548</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42579</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.45047</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.49288</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24978</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27013</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.19219</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.27599</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.44269</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.54859</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.43944</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.40273</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43444</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.68964</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5094</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22143</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31143</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28355</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31445</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.56868</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.91473</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.9073600000000001</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.89924</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.90566</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.90042</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.9111900000000001</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.5835499999999999</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>1.19634</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38591</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.71985</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.8085</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3497</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.50064</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.68984</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41153</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65646</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.77291</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45242</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28107</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45836</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34452</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4111</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3763</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.2657</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14842</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28314</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19913</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25604</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27922</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.2156</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25445</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27677</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28936</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28967</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.20262</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43478</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.6881799999999999</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.91384</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.87061</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.88018</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.7620399999999999</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.09442</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.49029</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.09106</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.82472</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.64806</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.55486</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.6593300000000001</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.51358</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.63044</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37484</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36017</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48957</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5279299999999999</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4804</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48401</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41682</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40276</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41009</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41643</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39455</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41038</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40848</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39426</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41913</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41718</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45088</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44938</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56101</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50105</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45099</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.49259</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44856</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45046</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.40693</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44383</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43515</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5223300000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43294</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.39492</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40752</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.63214</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.28233</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.4122</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43665</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49304</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43895</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.77558</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.92303</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.8172</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.9655199999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.98703</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.22404</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80892</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.58378</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5256799999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8339299999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76966</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62339</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6719700000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44112</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47204</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.4826</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47715</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46977</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41733</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55235</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4419</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45585</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42415</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44566</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41584</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45511</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.3976</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40467</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39658</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37791</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37303</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38686</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39895</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39485</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33776</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.1935</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40288</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4543</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39754</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4641</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.10779</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18101</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43311</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41556</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40993</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37609</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36617</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44508</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39675</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32257</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27061</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22702</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28665</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22931</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24873</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.2455</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14096</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29686</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24461</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04335</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25012</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27779</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16841</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18678</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27394</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23355</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25838</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23356</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27627</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36996</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34985</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.3083399999999999</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.21657</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.28051</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.26482</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01795</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00299</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15179</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02547</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01485</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02431</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.02985</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00118</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28172</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03414</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01581</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03525</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.2075</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27296</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27968</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.46012</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.36538</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.88261</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.7892</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.4301</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.55326</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.45688</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.49132</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.40373</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.36699</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.41655</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.44688</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.41008</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.42292</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.91077</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.00222</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.9010499999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.89039</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.1499</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27371</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.12447</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.05273</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29159</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.004059999999999999</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28716</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00168</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06911</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.40302</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32307</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.22705</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.44683</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.49993</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.52228</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.40805</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.46671</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38811</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.43396</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.42611</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14079</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27489</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27005</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3302</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.43855</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46607</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.42578</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.49001</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25324</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.38991</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.38613</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.4712</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.47531</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41116</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.4614</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.40357</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.4715299999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.59048</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.40661</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37415</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45652</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.2443</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36765</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47654</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39117</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26113</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.40715</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42638</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42535</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50016</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.57565</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.57662</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.46915</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.59949</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.65273</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49663</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5307799999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5763200000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.48938</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6424</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.79476</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7179500000000001</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.5745800000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.53561</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.51964</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39751</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44133</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39565</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37191</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36509</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34594</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.39725</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.38771</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.39135</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.15021</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.25785</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28732</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.06189</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.14996</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.12441</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.20584</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.15529</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25968</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15057</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05617</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.05454</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07353</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.20369</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.07748999999999999</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05631</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.21663</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.19056</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36613</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38928</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41021</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.47396</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.44567</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41767</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.41632</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42857</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3817</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38257</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.03899</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.56945</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.51117</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40498</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.45817</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.39595</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.38853</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38183</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.38687</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.22046</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.11776</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.11984</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.1224</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.13642</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.24462</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.11089</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01764</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.24372</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.05579</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.11772</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.23829</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.27478</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.40385</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.22985</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.39769</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43248</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41338</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40627</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39663</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4055</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38479</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36823</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.44847</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39526</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38161</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1799</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14948</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.20415</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.13829</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.27496</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04597</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.09931999999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.13082</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.13124</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.19578</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.11673</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.13207</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.15567</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.25237</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.23338</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27274</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15849</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36979</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.16122</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.23032</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20437</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14834</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25509</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.40314</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40533</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47772</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.3895</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39129</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.39275</v>
       </c>
     </row>
   </sheetData>
